--- a/docs/UserStory_QuickOrder_v0.1.xlsx
+++ b/docs/UserStory_QuickOrder_v0.1.xlsx
@@ -1955,7 +1955,7 @@
       </c>
       <c r="M21" s="22" t="inlineStr">
         <is>
-          <t>Chưa làm</t>
+          <t>Hoàn thành</t>
         </is>
       </c>
     </row>
@@ -2020,7 +2020,7 @@
       </c>
       <c r="M22" s="22" t="inlineStr">
         <is>
-          <t>Chưa làm</t>
+          <t>Hoàn thành</t>
         </is>
       </c>
     </row>
@@ -3336,7 +3336,7 @@
       </c>
       <c r="M42" s="22" t="inlineStr">
         <is>
-          <t>Chưa làm</t>
+          <t>Hoàn thành</t>
         </is>
       </c>
     </row>
@@ -3402,7 +3402,7 @@
       </c>
       <c r="M43" s="22" t="inlineStr">
         <is>
-          <t>Chưa làm</t>
+          <t>Hoàn thành</t>
         </is>
       </c>
     </row>
@@ -3599,7 +3599,7 @@
       </c>
       <c r="M46" s="22" t="inlineStr">
         <is>
-          <t>Chưa làm</t>
+          <t>Hoàn thành</t>
         </is>
       </c>
     </row>

--- a/docs/UserStory_QuickOrder_v0.1.xlsx
+++ b/docs/UserStory_QuickOrder_v0.1.xlsx
@@ -736,7 +736,7 @@
       </c>
       <c r="G3" s="21" t="inlineStr">
         <is>
-          <t>1. Cho tôi chưa đăng nhập, khi đăng ký với vai trò Khách hàng và thông tin hợp lệ, thì tài khoản được tạo.
+          <t>1. Cho tôi chưa đăng nhập, khi đăng ký tài khoản khách với thông tin hợp lệ và nhập đúng mã 6 số gửi qua email, thì tài khoản được tạo và tôi được đăng nhập.
 2. Gọi món qua mã QR vẫn không yêu cầu tài khoản.</t>
         </is>
       </c>
@@ -765,7 +765,7 @@
       </c>
       <c r="M3" s="22" t="inlineStr">
         <is>
-          <t>Chưa làm</t>
+          <t>Hoàn thành</t>
         </is>
       </c>
     </row>
@@ -1794,9 +1794,10 @@
       </c>
       <c r="G19" s="21" t="inlineStr">
         <is>
-          <t>1. Cho tôi đã đăng nhập, khi mở "Lịch sử đơn", thì thấy danh sách đơn mới nhất trước.
+          <t>1. Cho tôi đã đăng nhập, khi mở "Lịch sử", thì thấy danh sách đơn mới nhất trước.
 2. Khi mở một đơn, thì thấy chi tiết món và tổng tiền.
-3. Cho chưa có đơn nào, thì hệ thống báo "Bạn chưa có đơn nào".</t>
+3. Cho chưa có đơn nào, thì hệ thống báo "Chưa có đơn nào trong tài khoản".
+4. Đơn đặt khi chưa đăng nhập có thể lưu vào tài khoản bằng mã riêng của đơn trên đúng trình duyệt đã đặt.</t>
         </is>
       </c>
       <c r="H19" s="22" t="inlineStr">
@@ -1824,7 +1825,7 @@
       </c>
       <c r="M19" s="22" t="inlineStr">
         <is>
-          <t>Chưa làm</t>
+          <t>Hoàn thành</t>
         </is>
       </c>
     </row>
@@ -1889,7 +1890,7 @@
       </c>
       <c r="M20" s="22" t="inlineStr">
         <is>
-          <t>Chưa làm</t>
+          <t>Hoàn thành</t>
         </is>
       </c>
     </row>
@@ -2086,7 +2087,7 @@
       </c>
       <c r="M23" s="22" t="inlineStr">
         <is>
-          <t>Chưa làm</t>
+          <t>Hoàn thành</t>
         </is>
       </c>
     </row>
@@ -2122,9 +2123,9 @@
       </c>
       <c r="G24" s="21" t="inlineStr">
         <is>
-          <t>1. Cho tôi mở một đơn, khi nhập nội dung và gửi, thì khiếu nại được lưu ở trạng thái Mới.
-2. Cho nội dung trống, thì hệ thống báo lỗi và không gửi.
-3. Tôi xem được trạng thái xử lý và phản hồi của Admin.</t>
+          <t>1. Cho tôi mở một đơn, khi nhập nội dung (10 đến 500 ký tự) và gửi, thì khiếu nại được lưu ở trạng thái Mới.
+2. Cho nội dung quá ngắn hoặc trống, thì hệ thống báo lỗi và không gửi.
+3. Tôi xem được trạng thái xử lý và phản hồi của chủ quán.</t>
         </is>
       </c>
       <c r="H24" s="22" t="inlineStr">
@@ -2152,7 +2153,7 @@
       </c>
       <c r="M24" s="22" t="inlineStr">
         <is>
-          <t>Chưa làm</t>
+          <t>Hoàn thành</t>
         </is>
       </c>
     </row>
@@ -3438,9 +3439,9 @@
       </c>
       <c r="G44" s="21" t="inlineStr">
         <is>
-          <t>1. Cho tôi chọn khoảng thời gian, thì hệ thống hiển thị tổng doanh thu, số đơn và biểu đồ theo ngày.
+          <t>1. Cho tôi chọn khoảng thời gian (hôm nay, 7 ngày, 30 ngày, tháng này), thì hệ thống hiển thị tổng doanh thu, số đơn và biểu đồ theo ngày.
 2. Chỉ tính các đơn Hoàn thành.
-3. Cho không có dữ liệu, thì hiển thị "Chưa có số liệu".</t>
+3. Cho không có dữ liệu, thì các số liệu hiển thị bằng 0.</t>
         </is>
       </c>
       <c r="H44" s="22" t="inlineStr">
@@ -3468,7 +3469,7 @@
       </c>
       <c r="M44" s="22" t="inlineStr">
         <is>
-          <t>Chưa làm</t>
+          <t>Hoàn thành</t>
         </is>
       </c>
     </row>
@@ -3505,7 +3506,7 @@
       <c r="G45" s="21" t="inlineStr">
         <is>
           <t>1. Cho tôi chọn khoảng thời gian, thì hệ thống xếp hạng món theo số lượng bán.
-2. Cho không có dữ liệu, thì hiển thị "Chưa có số liệu".</t>
+2. Cho không có món nào bán ra trong kỳ, thì hiển thị "Chưa có món bán ra trong kỳ này".</t>
         </is>
       </c>
       <c r="H45" s="22" t="inlineStr">
@@ -3533,7 +3534,7 @@
       </c>
       <c r="M45" s="22" t="inlineStr">
         <is>
-          <t>Chưa làm</t>
+          <t>Hoàn thành</t>
         </is>
       </c>
     </row>
@@ -3702,8 +3703,8 @@
       </c>
       <c r="G48" s="21" t="inlineStr">
         <is>
-          <t>1. Cho tôi khóa quán kèm lý do, thì mã QR của quán báo "Quán tạm ngưng nhận món".
-2. Cho tôi mở khóa, thì quán nhận đơn bình thường trở lại.
+          <t>1. Cho tôi khóa quán kèm lý do, thì khách mở mã QR của quán sẽ thấy quán không còn hoạt động và không đặt được món.
+2. Cho tôi mở khóa, thì quán nhận đơn bình thường trở lại và mã QR cũ dùng được.
 3. Các đơn cũ của quán vẫn được giữ.</t>
         </is>
       </c>
@@ -3732,7 +3733,7 @@
       </c>
       <c r="M48" s="22" t="inlineStr">
         <is>
-          <t>Chưa làm</t>
+          <t>Hoàn thành</t>
         </is>
       </c>
     </row>
@@ -3798,7 +3799,7 @@
       </c>
       <c r="M49" s="22" t="inlineStr">
         <is>
-          <t>Chưa làm</t>
+          <t>Hoàn thành</t>
         </is>
       </c>
     </row>
@@ -3864,7 +3865,7 @@
       </c>
       <c r="M50" s="22" t="inlineStr">
         <is>
-          <t>Chưa làm</t>
+          <t>Hoàn thành</t>
         </is>
       </c>
     </row>
@@ -3900,8 +3901,8 @@
       </c>
       <c r="G51" s="21" t="inlineStr">
         <is>
-          <t>1. Hệ thống hiển thị số quán theo trạng thái, số người dùng, số đơn và doanh thu theo khoảng thời gian chọn.
-2. Cho không có dữ liệu, thì hiển thị "Chưa có số liệu".</t>
+          <t>1. Hệ thống hiển thị tổng số quán, số người dùng, số đơn và doanh thu của toàn bộ thời gian.
+2. Doanh thu chỉ tính các đơn Hoàn thành.</t>
         </is>
       </c>
       <c r="H51" s="22" t="inlineStr">
@@ -3929,7 +3930,7 @@
       </c>
       <c r="M51" s="22" t="inlineStr">
         <is>
-          <t>Chưa làm</t>
+          <t>Hoàn thành</t>
         </is>
       </c>
     </row>
@@ -3946,12 +3947,12 @@
       </c>
       <c r="C52" s="21" t="inlineStr">
         <is>
-          <t>Quản trị viên</t>
+          <t>Chủ quán</t>
         </is>
       </c>
       <c r="D52" s="21" t="inlineStr">
         <is>
-          <t>xem và phản hồi khiếu nại của khách</t>
+          <t>xem và phản hồi khiếu nại của khách về quán của mình</t>
         </is>
       </c>
       <c r="E52" s="21" t="inlineStr">
@@ -3965,8 +3966,9 @@
       </c>
       <c r="G52" s="21" t="inlineStr">
         <is>
-          <t>1. Cho có khiếu nại mới, thì tôi mở xem được nội dung và đơn liên quan.
-2. Cho tôi nhập phản hồi và chuyển sang Đã xử lý, thì khách thấy phản hồi và trạng thái.</t>
+          <t>1. Cho có khiếu nại mới về quán của tôi, thì tôi mở xem được nội dung và đơn liên quan.
+2. Cho tôi nhập phản hồi rồi đóng khiếu nại, thì khách thấy phản hồi và trạng thái.
+3. Chủ quán khác không xem hoặc sửa được khiếu nại này.</t>
         </is>
       </c>
       <c r="H52" s="22" t="inlineStr">
@@ -3994,7 +3996,7 @@
       </c>
       <c r="M52" s="22" t="inlineStr">
         <is>
-          <t>Chưa làm</t>
+          <t>Hoàn thành</t>
         </is>
       </c>
     </row>
